--- a/ejemplos/vuelos_ficticios.xlsx
+++ b/ejemplos/vuelos_ficticios.xlsx
@@ -469,12 +469,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FR6305</t>
+          <t>XX6305</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -506,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FR3471</t>
+          <t>XX3471</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,7 +518,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FR7468</t>
+          <t>XX7468</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -553,7 +550,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FR1791</t>
+          <t>XX1791</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -568,7 +565,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FR2186</t>
+          <t>XX2186</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -600,7 +597,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FR9779</t>
+          <t>XX9779</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -615,7 +612,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FR2542</t>
+          <t>XX2542</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -647,7 +644,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FR6991</t>
+          <t>XX6991</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -660,9 +657,6 @@
           <t>23:26</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>B738</t>
@@ -680,12 +674,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FR1950</t>
+          <t>XX1950</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -717,7 +708,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FR9313</t>
+          <t>XX9313</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -732,7 +723,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FR4517</t>
+          <t>XX4517</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FR1614</t>
+          <t>XX1614</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -779,7 +770,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FR2408</t>
+          <t>XX2408</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -811,7 +802,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FR8104</t>
+          <t>XX8104</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -824,9 +815,6 @@
           <t>17:48</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>B738</t>
@@ -844,12 +832,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FR7851</t>
+          <t>XX7851</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -881,7 +866,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FR2144</t>
+          <t>XX2144</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -896,7 +881,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FR4943</t>
+          <t>XX4943</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -928,7 +913,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FR2486</t>
+          <t>XX2486</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -943,7 +928,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FR7955</t>
+          <t>XX7955</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -975,7 +960,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FR1968</t>
+          <t>XX1968</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -988,9 +973,6 @@
           <t>20:07</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>B738</t>
@@ -1008,12 +990,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FR3028</t>
+          <t>XX3028</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1045,7 +1024,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FR4657</t>
+          <t>XX4657</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1060,7 +1039,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FR2013</t>
+          <t>XX2013</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1092,7 +1071,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FR7499</t>
+          <t>XX7499</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1107,7 +1086,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FR1812</t>
+          <t>XX1812</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1139,7 +1118,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FR4622</t>
+          <t>XX4622</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1152,9 +1131,6 @@
           <t>18:14</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>B738</t>
@@ -1172,12 +1148,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FR1763</t>
+          <t>XX1763</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1209,7 +1182,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FR3181</t>
+          <t>XX3181</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1224,7 +1197,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FR5744</t>
+          <t>XX5744</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1256,7 +1229,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FR7867</t>
+          <t>XX7867</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1271,7 +1244,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FR3363</t>
+          <t>XX3363</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1303,7 +1276,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FR9858</t>
+          <t>XX9858</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1316,9 +1289,6 @@
           <t>19:29</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -1336,12 +1306,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FR2929</t>
+          <t>XX2929</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1373,7 +1340,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FR6054</t>
+          <t>XX6054</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1388,7 +1355,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FR3961</t>
+          <t>XX3961</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1420,7 +1387,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FR2688</t>
+          <t>XX2688</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1435,7 +1402,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FR4078</t>
+          <t>XX4078</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1465,12 +1432,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FR7101</t>
+          <t>XX7101</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1502,7 +1466,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FR2596</t>
+          <t>XX2596</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1517,7 +1481,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FR2028</t>
+          <t>XX2028</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1549,7 +1513,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FR1976</t>
+          <t>XX1976</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1564,7 +1528,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FR4374</t>
+          <t>XX4374</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1596,7 +1560,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FR9133</t>
+          <t>XX9133</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1609,9 +1573,6 @@
           <t>20:15</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>B738</t>
@@ -1629,12 +1590,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FR9711</t>
+          <t>XX9711</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1666,7 +1624,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FR8005</t>
+          <t>XX8005</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1681,7 +1639,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FR6146</t>
+          <t>XX6146</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1713,7 +1671,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FR8628</t>
+          <t>XX8628</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1728,7 +1686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FR8424</t>
+          <t>XX8424</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1758,12 +1716,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FR6924</t>
+          <t>XX6924</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1795,7 +1750,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FR5911</t>
+          <t>XX5911</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1810,7 +1765,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FR5070</t>
+          <t>XX5070</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1842,7 +1797,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FR3945</t>
+          <t>XX3945</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1857,7 +1812,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FR4999</t>
+          <t>XX4999</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1889,7 +1844,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FR2341</t>
+          <t>XX2341</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1902,9 +1857,6 @@
           <t>18:47</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>B738</t>
@@ -1922,12 +1874,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FR5919</t>
+          <t>XX5919</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1959,7 +1908,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FR9604</t>
+          <t>XX9604</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1974,7 +1923,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FR9111</t>
+          <t>XX9111</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2006,7 +1955,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FR6627</t>
+          <t>XX6627</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2021,7 +1970,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FR8353</t>
+          <t>XX8353</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2053,7 +2002,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FR5717</t>
+          <t>XX5717</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2068,7 +2017,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FR2199</t>
+          <t>XX2199</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2100,7 +2049,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FR2934</t>
+          <t>XX2934</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2113,9 +2062,6 @@
           <t>21:18</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>B738</t>
@@ -2133,12 +2079,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FR9387</t>
+          <t>XX9387</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2170,7 +2113,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FR7850</t>
+          <t>XX7850</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2185,7 +2128,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FR3702</t>
+          <t>XX3702</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2217,7 +2160,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FR6604</t>
+          <t>XX6604</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2232,7 +2175,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FR3490</t>
+          <t>XX3490</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2264,7 +2207,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FR9011</t>
+          <t>XX9011</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2277,9 +2220,6 @@
           <t>20:13</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -2297,12 +2237,9 @@
           <t>12/07/2027</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FR7909</t>
+          <t>XX7909</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2334,7 +2271,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FR1642</t>
+          <t>XX1642</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2349,7 +2286,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FR2271</t>
+          <t>XX2271</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2381,7 +2318,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FR6140</t>
+          <t>XX6140</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2394,9 +2331,6 @@
           <t>16:46</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>B738</t>
@@ -2416,7 +2350,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FR6572</t>
+          <t>XX6572</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2431,7 +2365,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FR6737</t>
+          <t>XX6737</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2463,7 +2397,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FR9137</t>
+          <t>XX9137</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2478,7 +2412,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FR8474</t>
+          <t>XX8474</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2510,7 +2444,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FR2126</t>
+          <t>XX2126</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2525,7 +2459,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FR2533</t>
+          <t>XX2533</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2557,7 +2491,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FR5422</t>
+          <t>XX5422</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2572,7 +2506,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FR8767</t>
+          <t>XX8767</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2604,7 +2538,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FR2064</t>
+          <t>XX2064</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2619,7 +2553,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FR1994</t>
+          <t>XX1994</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2651,7 +2585,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FR6072</t>
+          <t>XX6072</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2666,7 +2600,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FR8301</t>
+          <t>XX8301</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2698,7 +2632,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FR5662</t>
+          <t>XX5662</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2713,7 +2647,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FR7320</t>
+          <t>XX7320</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2745,7 +2679,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FR6685</t>
+          <t>XX6685</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2760,7 +2694,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FR1369</t>
+          <t>XX1369</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2792,7 +2726,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FR8564</t>
+          <t>XX8564</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2807,7 +2741,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FR6823</t>
+          <t>XX6823</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2839,7 +2773,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FR3753</t>
+          <t>XX3753</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2854,7 +2788,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FR2918</t>
+          <t>XX2918</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2886,7 +2820,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FR9088</t>
+          <t>XX9088</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2901,7 +2835,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FR1965</t>
+          <t>XX1965</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2933,7 +2867,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FR4575</t>
+          <t>XX4575</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2948,7 +2882,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FR5709</t>
+          <t>XX5709</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2980,7 +2914,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FR3119</t>
+          <t>XX3119</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2995,7 +2929,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FR5056</t>
+          <t>XX5056</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3027,7 +2961,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FR7519</t>
+          <t>XX7519</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3042,7 +2976,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FR7405</t>
+          <t>XX7405</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3074,7 +3008,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FR9134</t>
+          <t>XX9134</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3089,7 +3023,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FR2320</t>
+          <t>XX2320</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3121,7 +3055,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FR3725</t>
+          <t>XX3725</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3136,7 +3070,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FR8359</t>
+          <t>XX8359</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3168,7 +3102,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FR7580</t>
+          <t>XX7580</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3183,7 +3117,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FR5552</t>
+          <t>XX5552</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3215,7 +3149,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FR3243</t>
+          <t>XX3243</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3230,7 +3164,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FR8053</t>
+          <t>XX8053</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3262,7 +3196,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FR5561</t>
+          <t>XX5561</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3277,7 +3211,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FR7804</t>
+          <t>XX7804</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3309,7 +3243,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FR6878</t>
+          <t>XX6878</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3324,7 +3258,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FR7233</t>
+          <t>XX7233</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3356,7 +3290,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FR4780</t>
+          <t>XX4780</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3371,7 +3305,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FR3472</t>
+          <t>XX3472</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3403,7 +3337,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FR2359</t>
+          <t>XX2359</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3418,7 +3352,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FR3887</t>
+          <t>XX3887</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3450,7 +3384,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FR3478</t>
+          <t>XX3478</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3465,7 +3399,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FR4800</t>
+          <t>XX4800</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3497,7 +3431,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FR4822</t>
+          <t>XX4822</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3512,7 +3446,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FR1197</t>
+          <t>XX1197</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3544,7 +3478,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FR8945</t>
+          <t>XX8945</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3559,7 +3493,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FR3987</t>
+          <t>XX3987</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3591,7 +3525,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FR5304</t>
+          <t>XX5304</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3606,7 +3540,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FR5619</t>
+          <t>XX5619</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3638,7 +3572,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FR1067</t>
+          <t>XX1067</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3653,7 +3587,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FR3386</t>
+          <t>XX3386</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3685,7 +3619,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FR7864</t>
+          <t>XX7864</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3700,7 +3634,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FR9758</t>
+          <t>XX9758</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3732,7 +3666,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FR7049</t>
+          <t>XX7049</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3747,7 +3681,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FR6220</t>
+          <t>XX6220</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3779,7 +3713,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FR3056</t>
+          <t>XX3056</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3794,7 +3728,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FR9445</t>
+          <t>XX9445</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3824,12 +3758,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FR1884</t>
+          <t>XX1884</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3861,7 +3792,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FR8481</t>
+          <t>XX8481</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3876,7 +3807,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FR7428</t>
+          <t>XX7428</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3908,7 +3839,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FR7521</t>
+          <t>XX7521</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3923,7 +3854,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FR7536</t>
+          <t>XX7536</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3955,7 +3886,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FR7457</t>
+          <t>XX7457</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3968,9 +3899,6 @@
           <t>18:51</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>B738</t>
@@ -3988,12 +3916,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FR2696</t>
+          <t>XX2696</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4025,7 +3950,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FR8889</t>
+          <t>XX8889</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4040,7 +3965,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FR7560</t>
+          <t>XX7560</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4072,7 +3997,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FR2019</t>
+          <t>XX2019</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4087,7 +4012,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FR4122</t>
+          <t>XX4122</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4119,7 +4044,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FR2103</t>
+          <t>XX2103</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4132,9 +4057,6 @@
           <t>19:04</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>B738</t>
@@ -4152,12 +4074,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FR4420</t>
+          <t>XX4420</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4189,7 +4108,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FR8219</t>
+          <t>XX8219</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4204,7 +4123,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FR3659</t>
+          <t>XX3659</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4236,7 +4155,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FR2801</t>
+          <t>XX2801</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4251,7 +4170,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FR6571</t>
+          <t>XX6571</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4283,7 +4202,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FR1861</t>
+          <t>XX1861</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4296,9 +4215,6 @@
           <t>18:21</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>B738</t>
@@ -4316,12 +4232,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FR2677</t>
+          <t>XX2677</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4353,7 +4266,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FR1003</t>
+          <t>XX1003</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4368,7 +4281,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FR9882</t>
+          <t>XX9882</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4400,7 +4313,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FR9791</t>
+          <t>XX9791</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4415,7 +4328,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FR2662</t>
+          <t>XX2662</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4447,7 +4360,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FR6957</t>
+          <t>XX6957</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4460,9 +4373,6 @@
           <t>17:05</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>B738</t>
@@ -4480,12 +4390,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FR1417</t>
+          <t>XX1417</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4517,7 +4424,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FR2152</t>
+          <t>XX2152</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4532,7 +4439,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FR4407</t>
+          <t>XX4407</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4564,7 +4471,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FR7164</t>
+          <t>XX7164</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4579,7 +4486,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FR3433</t>
+          <t>XX3433</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4611,7 +4518,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FR5132</t>
+          <t>XX5132</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4624,9 +4531,6 @@
           <t>20:41</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>B738</t>
@@ -4644,12 +4548,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FR6691</t>
+          <t>XX6691</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4681,7 +4582,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FR6966</t>
+          <t>XX6966</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4696,7 +4597,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FR8768</t>
+          <t>XX8768</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4728,7 +4629,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FR3012</t>
+          <t>XX3012</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4743,7 +4644,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FR2889</t>
+          <t>XX2889</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4775,7 +4676,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FR8996</t>
+          <t>XX8996</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4788,9 +4689,6 @@
           <t>19:59</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>B738</t>
@@ -4808,12 +4706,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FR8634</t>
+          <t>XX8634</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4845,7 +4740,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FR8870</t>
+          <t>XX8870</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4860,7 +4755,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FR8927</t>
+          <t>XX8927</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4892,7 +4787,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FR6109</t>
+          <t>XX6109</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4907,7 +4802,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FR2407</t>
+          <t>XX2407</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4939,7 +4834,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FR3361</t>
+          <t>XX3361</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4952,9 +4847,6 @@
           <t>19:21</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -4972,12 +4864,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>FR2674</t>
+          <t>XX2674</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5009,7 +4898,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FR6613</t>
+          <t>XX6613</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5024,7 +4913,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FR5337</t>
+          <t>XX5337</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5056,7 +4945,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FR8841</t>
+          <t>XX8841</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5071,7 +4960,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FR3645</t>
+          <t>XX3645</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5103,7 +4992,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FR9459</t>
+          <t>XX9459</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5116,9 +5005,6 @@
           <t>18:38</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>B738</t>
@@ -5136,12 +5022,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FR1378</t>
+          <t>XX1378</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5173,7 +5056,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FR4362</t>
+          <t>XX4362</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5188,7 +5071,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FR9654</t>
+          <t>XX9654</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5220,7 +5103,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FR6926</t>
+          <t>XX6926</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5235,7 +5118,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FR3401</t>
+          <t>XX3401</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5267,7 +5150,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FR1443</t>
+          <t>XX1443</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5282,7 +5165,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FR9652</t>
+          <t>XX9652</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5314,7 +5197,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FR5883</t>
+          <t>XX5883</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5327,9 +5210,6 @@
           <t>22:15</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>B738</t>
@@ -5347,12 +5227,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FR2491</t>
+          <t>XX2491</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5384,7 +5261,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FR5278</t>
+          <t>XX5278</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5399,7 +5276,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FR9493</t>
+          <t>XX9493</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5431,7 +5308,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FR7008</t>
+          <t>XX7008</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5446,7 +5323,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FR3736</t>
+          <t>XX3736</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5478,7 +5355,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FR6827</t>
+          <t>XX6827</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5491,9 +5368,6 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>B738</t>
@@ -5511,12 +5385,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FR4650</t>
+          <t>XX4650</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5548,7 +5419,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FR9725</t>
+          <t>XX9725</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5563,7 +5434,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FR9236</t>
+          <t>XX9236</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5595,7 +5466,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FR6401</t>
+          <t>XX6401</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5610,7 +5481,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FR4654</t>
+          <t>XX4654</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5642,7 +5513,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FR4197</t>
+          <t>XX4197</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5655,9 +5526,6 @@
           <t>20:55</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -5675,12 +5543,9 @@
           <t>13/07/2027</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FR4922</t>
+          <t>XX4922</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5712,7 +5577,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FR7564</t>
+          <t>XX7564</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5727,7 +5592,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FR4714</t>
+          <t>XX4714</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5759,7 +5624,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FR4275</t>
+          <t>XX4275</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5774,7 +5639,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FR9480</t>
+          <t>XX9480</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5806,7 +5671,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FR9073</t>
+          <t>XX9073</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5819,9 +5684,6 @@
           <t>19:22</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>B738</t>
@@ -5841,7 +5703,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FR6825</t>
+          <t>XX6825</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5856,7 +5718,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FR1474</t>
+          <t>XX1474</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5888,7 +5750,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FR1457</t>
+          <t>XX1457</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5903,7 +5765,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FR5577</t>
+          <t>XX5577</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5935,7 +5797,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FR8737</t>
+          <t>XX8737</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5950,7 +5812,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FR5246</t>
+          <t>XX5246</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5982,7 +5844,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FR4172</t>
+          <t>XX4172</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5997,7 +5859,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FR6640</t>
+          <t>XX6640</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6029,7 +5891,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>FR8327</t>
+          <t>XX8327</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6044,7 +5906,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FR6726</t>
+          <t>XX6726</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6076,7 +5938,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>FR6974</t>
+          <t>XX6974</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6091,7 +5953,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FR2319</t>
+          <t>XX2319</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6123,7 +5985,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>FR4612</t>
+          <t>XX4612</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6138,7 +6000,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FR2673</t>
+          <t>XX2673</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6170,7 +6032,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FR4716</t>
+          <t>XX4716</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6185,7 +6047,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FR8701</t>
+          <t>XX8701</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6217,7 +6079,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FR4222</t>
+          <t>XX4222</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6232,7 +6094,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FR6533</t>
+          <t>XX6533</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6264,7 +6126,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FR4348</t>
+          <t>XX4348</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6279,7 +6141,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FR8907</t>
+          <t>XX8907</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6311,7 +6173,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FR1031</t>
+          <t>XX1031</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6326,7 +6188,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FR8855</t>
+          <t>XX8855</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6358,7 +6220,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FR6636</t>
+          <t>XX6636</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6373,7 +6235,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FR2389</t>
+          <t>XX2389</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6405,7 +6267,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>FR2964</t>
+          <t>XX2964</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6420,7 +6282,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FR7365</t>
+          <t>XX7365</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6452,7 +6314,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>FR4265</t>
+          <t>XX4265</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6467,7 +6329,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FR8832</t>
+          <t>XX8832</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6499,7 +6361,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FR3924</t>
+          <t>XX3924</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6514,7 +6376,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FR8109</t>
+          <t>XX8109</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6546,7 +6408,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FR6447</t>
+          <t>XX6447</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6561,7 +6423,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FR2421</t>
+          <t>XX2421</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6593,7 +6455,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FR7485</t>
+          <t>XX7485</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6608,7 +6470,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FR8588</t>
+          <t>XX8588</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6640,7 +6502,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FR7576</t>
+          <t>XX7576</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6655,7 +6517,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FR2391</t>
+          <t>XX2391</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6687,7 +6549,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FR3602</t>
+          <t>XX3602</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6702,7 +6564,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FR3785</t>
+          <t>XX3785</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6734,7 +6596,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FR3081</t>
+          <t>XX3081</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6749,7 +6611,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FR1451</t>
+          <t>XX1451</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6781,7 +6643,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FR3476</t>
+          <t>XX3476</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6796,7 +6658,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FR8624</t>
+          <t>XX8624</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6828,7 +6690,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FR3394</t>
+          <t>XX3394</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6843,7 +6705,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FR8771</t>
+          <t>XX8771</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6875,7 +6737,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FR6741</t>
+          <t>XX6741</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6890,7 +6752,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FR3554</t>
+          <t>XX3554</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6922,7 +6784,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>FR3146</t>
+          <t>XX3146</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6937,7 +6799,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FR1350</t>
+          <t>XX1350</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6969,7 +6831,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>FR1233</t>
+          <t>XX1233</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6984,7 +6846,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FR2683</t>
+          <t>XX2683</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7016,7 +6878,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FR9627</t>
+          <t>XX9627</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7031,7 +6893,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FR3281</t>
+          <t>XX3281</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7063,7 +6925,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>FR8107</t>
+          <t>XX8107</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7078,7 +6940,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FR4191</t>
+          <t>XX4191</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7110,7 +6972,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FR4457</t>
+          <t>XX4457</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7125,7 +6987,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FR1458</t>
+          <t>XX1458</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7157,7 +7019,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>FR5126</t>
+          <t>XX5126</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7172,7 +7034,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FR4486</t>
+          <t>XX4486</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7204,7 +7066,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FR5799</t>
+          <t>XX5799</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7219,7 +7081,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FR9211</t>
+          <t>XX9211</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7249,12 +7111,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FR4940</t>
+          <t>XX4940</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7286,7 +7145,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FR6341</t>
+          <t>XX6341</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7301,7 +7160,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FR5249</t>
+          <t>XX5249</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7333,7 +7192,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FR7865</t>
+          <t>XX7865</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7348,7 +7207,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FR3147</t>
+          <t>XX3147</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7380,7 +7239,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FR1997</t>
+          <t>XX1997</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7393,9 +7252,6 @@
           <t>20:51</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
           <t>B738</t>
@@ -7413,12 +7269,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>FR6796</t>
+          <t>XX6796</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7450,7 +7303,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FR8506</t>
+          <t>XX8506</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7465,7 +7318,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>FR9466</t>
+          <t>XX9466</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7497,7 +7350,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FR7891</t>
+          <t>XX7891</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7512,7 +7365,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FR9219</t>
+          <t>XX9219</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7544,7 +7397,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FR3142</t>
+          <t>XX3142</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7557,9 +7410,6 @@
           <t>17:10</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
           <t>B738</t>
@@ -7577,12 +7427,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>FR9713</t>
+          <t>XX9713</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7614,7 +7461,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FR3487</t>
+          <t>XX3487</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7629,7 +7476,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FR9577</t>
+          <t>XX9577</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7661,7 +7508,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FR9364</t>
+          <t>XX9364</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7676,7 +7523,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>FR1306</t>
+          <t>XX1306</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7708,7 +7555,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FR8211</t>
+          <t>XX8211</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7721,9 +7568,6 @@
           <t>18:04</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>B738</t>
@@ -7741,12 +7585,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>FR4000</t>
+          <t>XX4000</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7778,7 +7619,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FR1064</t>
+          <t>XX1064</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7793,7 +7634,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>FR3454</t>
+          <t>XX3454</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7825,7 +7666,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FR3823</t>
+          <t>XX3823</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -7840,7 +7681,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>FR3319</t>
+          <t>XX3319</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7872,7 +7713,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FR8757</t>
+          <t>XX8757</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7885,9 +7726,6 @@
           <t>18:23</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
           <t>B738</t>
@@ -7905,12 +7743,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FR2971</t>
+          <t>XX2971</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7942,7 +7777,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FR2011</t>
+          <t>XX2011</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -7957,7 +7792,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FR6340</t>
+          <t>XX6340</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7989,7 +7824,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FR9492</t>
+          <t>XX9492</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8004,7 +7839,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>FR9695</t>
+          <t>XX9695</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -8036,7 +7871,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FR8905</t>
+          <t>XX8905</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8049,9 +7884,6 @@
           <t>19:21</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>B738</t>
@@ -8069,12 +7901,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FR2738</t>
+          <t>XX2738</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8106,7 +7935,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FR1930</t>
+          <t>XX1930</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8121,7 +7950,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FR5071</t>
+          <t>XX5071</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8153,7 +7982,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FR4134</t>
+          <t>XX4134</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8168,7 +7997,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FR5537</t>
+          <t>XX5537</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8200,7 +8029,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>FR1691</t>
+          <t>XX1691</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8213,9 +8042,6 @@
           <t>18:02</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
           <t>B738</t>
@@ -8233,12 +8059,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>FR2601</t>
+          <t>XX2601</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8270,7 +8093,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FR9318</t>
+          <t>XX9318</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8285,7 +8108,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>FR8408</t>
+          <t>XX8408</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -8317,7 +8140,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FR1456</t>
+          <t>XX1456</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8332,7 +8155,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>FR2038</t>
+          <t>XX2038</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8362,12 +8185,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>FR8262</t>
+          <t>XX8262</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -8399,7 +8219,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FR6334</t>
+          <t>XX6334</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8414,7 +8234,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FR9282</t>
+          <t>XX9282</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8446,7 +8266,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>FR9391</t>
+          <t>XX9391</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8461,7 +8281,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>FR4267</t>
+          <t>XX4267</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8493,7 +8313,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>FR5541</t>
+          <t>XX5541</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8506,9 +8326,6 @@
           <t>17:42</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
           <t>B738</t>
@@ -8526,12 +8343,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>FR8411</t>
+          <t>XX8411</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8563,7 +8377,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FR9325</t>
+          <t>XX9325</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8578,7 +8392,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FR9765</t>
+          <t>XX9765</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8610,7 +8424,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>FR9319</t>
+          <t>XX9319</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -8625,7 +8439,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FR5057</t>
+          <t>XX5057</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8657,7 +8471,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>FR9572</t>
+          <t>XX9572</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8670,9 +8484,6 @@
           <t>20:19</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
           <t>B738</t>
@@ -8690,12 +8501,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>FR5253</t>
+          <t>XX5253</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8727,7 +8535,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>FR4319</t>
+          <t>XX4319</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -8742,7 +8550,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>FR8332</t>
+          <t>XX8332</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8774,7 +8582,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>FR3246</t>
+          <t>XX3246</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -8789,7 +8597,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>FR7826</t>
+          <t>XX7826</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8821,7 +8629,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>FR2992</t>
+          <t>XX2992</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8834,9 +8642,6 @@
           <t>20:18</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
           <t>B738</t>
@@ -8854,12 +8659,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>FR9864</t>
+          <t>XX9864</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -8891,7 +8693,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>FR8243</t>
+          <t>XX8243</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8906,7 +8708,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>FR6177</t>
+          <t>XX6177</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8938,7 +8740,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>FR2188</t>
+          <t>XX2188</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8953,7 +8755,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>FR4942</t>
+          <t>XX4942</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -8985,7 +8787,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>FR8017</t>
+          <t>XX8017</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8998,9 +8800,6 @@
           <t>19:01</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>B738</t>
@@ -9018,12 +8817,9 @@
           <t>14/07/2027</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>FR2198</t>
+          <t>XX2198</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -9055,7 +8851,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>FR4484</t>
+          <t>XX4484</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9070,7 +8866,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FR5960</t>
+          <t>XX5960</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -9102,7 +8898,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>FR3004</t>
+          <t>XX3004</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9117,7 +8913,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>FR3530</t>
+          <t>XX3530</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -9149,7 +8945,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>FR6999</t>
+          <t>XX6999</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9162,9 +8958,6 @@
           <t>18:16</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
           <t>B738</t>
@@ -9184,7 +8977,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>FR3342</t>
+          <t>XX3342</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9199,7 +8992,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>FR5146</t>
+          <t>XX5146</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -9231,7 +9024,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>FR3248</t>
+          <t>XX3248</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9246,7 +9039,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>FR8663</t>
+          <t>XX8663</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -9278,7 +9071,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FR4597</t>
+          <t>XX4597</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9293,7 +9086,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>FR9992</t>
+          <t>XX9992</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -9325,7 +9118,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FR7525</t>
+          <t>XX7525</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9340,7 +9133,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FR8983</t>
+          <t>XX8983</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -9372,7 +9165,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FR3667</t>
+          <t>XX3667</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9387,7 +9180,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>FR4665</t>
+          <t>XX4665</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -9419,7 +9212,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FR9820</t>
+          <t>XX9820</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9434,7 +9227,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>FR8070</t>
+          <t>XX8070</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9466,7 +9259,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FR9447</t>
+          <t>XX9447</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9481,7 +9274,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>FR7616</t>
+          <t>XX7616</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -9513,7 +9306,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>FR6556</t>
+          <t>XX6556</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9528,7 +9321,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>FR7902</t>
+          <t>XX7902</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -9560,7 +9353,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>FR4207</t>
+          <t>XX4207</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9575,7 +9368,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>FR6842</t>
+          <t>XX6842</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9607,7 +9400,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FR6218</t>
+          <t>XX6218</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9622,7 +9415,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>FR2510</t>
+          <t>XX2510</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9654,7 +9447,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FR6995</t>
+          <t>XX6995</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9669,7 +9462,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>FR1319</t>
+          <t>XX1319</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9701,7 +9494,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>FR6537</t>
+          <t>XX6537</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9716,7 +9509,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>FR8514</t>
+          <t>XX8514</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -9748,7 +9541,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>FR8216</t>
+          <t>XX8216</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9763,7 +9556,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>FR1296</t>
+          <t>XX1296</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -9795,7 +9588,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>FR7297</t>
+          <t>XX7297</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9810,7 +9603,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>FR6431</t>
+          <t>XX6431</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9842,7 +9635,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>FR9477</t>
+          <t>XX9477</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9857,7 +9650,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>FR5840</t>
+          <t>XX5840</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -9889,7 +9682,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>FR9392</t>
+          <t>XX9392</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9904,7 +9697,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>FR2053</t>
+          <t>XX2053</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -9936,7 +9729,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>FR2848</t>
+          <t>XX2848</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -9951,7 +9744,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>FR4744</t>
+          <t>XX4744</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9983,7 +9776,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>FR2716</t>
+          <t>XX2716</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -9998,7 +9791,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>FR2377</t>
+          <t>XX2377</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -10030,7 +9823,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>FR5351</t>
+          <t>XX5351</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10045,7 +9838,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>FR5455</t>
+          <t>XX5455</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -10077,7 +9870,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>FR1648</t>
+          <t>XX1648</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10092,7 +9885,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>FR3974</t>
+          <t>XX3974</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -10124,7 +9917,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>FR5430</t>
+          <t>XX5430</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10139,7 +9932,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>FR3122</t>
+          <t>XX3122</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -10171,7 +9964,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>FR7918</t>
+          <t>XX7918</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10186,7 +9979,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>FR5237</t>
+          <t>XX5237</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -10218,7 +10011,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>FR7651</t>
+          <t>XX7651</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10233,7 +10026,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>FR3447</t>
+          <t>XX3447</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -10265,7 +10058,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>FR9434</t>
+          <t>XX9434</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10280,7 +10073,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>FR9103</t>
+          <t>XX9103</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -10312,7 +10105,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>FR6358</t>
+          <t>XX6358</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10327,7 +10120,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>FR2465</t>
+          <t>XX2465</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -10359,7 +10152,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>FR5572</t>
+          <t>XX5572</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -10374,7 +10167,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>FR1942</t>
+          <t>XX1942</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -10406,7 +10199,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>FR4003</t>
+          <t>XX4003</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -10421,7 +10214,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>FR7968</t>
+          <t>XX7968</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -10453,7 +10246,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>FR9994</t>
+          <t>XX9994</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -10468,7 +10261,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>FR5406</t>
+          <t>XX5406</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -10500,7 +10293,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>FR1275</t>
+          <t>XX1275</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -10515,7 +10308,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>FR2451</t>
+          <t>XX2451</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -10547,7 +10340,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>FR5268</t>
+          <t>XX5268</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -10562,7 +10355,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>FR2372</t>
+          <t>XX2372</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10592,12 +10385,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
-          <t>FR4643</t>
+          <t>XX4643</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -10629,7 +10419,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>FR2091</t>
+          <t>XX2091</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -10644,7 +10434,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>FR5332</t>
+          <t>XX5332</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10676,7 +10466,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>FR2993</t>
+          <t>XX2993</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -10691,7 +10481,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>FR8434</t>
+          <t>XX8434</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -10723,7 +10513,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>FR1189</t>
+          <t>XX1189</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -10736,9 +10526,6 @@
           <t>19:25</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -10756,12 +10543,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>FR9647</t>
+          <t>XX9647</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -10793,7 +10577,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>FR7844</t>
+          <t>XX7844</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -10808,7 +10592,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>FR5388</t>
+          <t>XX5388</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -10840,7 +10624,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>FR3117</t>
+          <t>XX3117</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -10855,7 +10639,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>FR1707</t>
+          <t>XX1707</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -10887,7 +10671,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>FR4906</t>
+          <t>XX4906</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -10900,9 +10684,6 @@
           <t>20:29</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
           <t>B738</t>
@@ -10920,12 +10701,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr"/>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>FR2793</t>
+          <t>XX2793</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -10957,7 +10735,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>FR9651</t>
+          <t>XX9651</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -10972,7 +10750,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>FR5290</t>
+          <t>XX5290</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -11004,7 +10782,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>FR1825</t>
+          <t>XX1825</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -11019,7 +10797,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>FR3967</t>
+          <t>XX3967</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -11051,7 +10829,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>FR4305</t>
+          <t>XX4305</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -11064,9 +10842,6 @@
           <t>17:26</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
           <t>B738</t>
@@ -11084,12 +10859,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr"/>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>FR6111</t>
+          <t>XX6111</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -11121,7 +10893,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>FR5997</t>
+          <t>XX5997</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -11136,7 +10908,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>FR4372</t>
+          <t>XX4372</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -11168,7 +10940,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>FR5750</t>
+          <t>XX5750</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -11183,7 +10955,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>FR8302</t>
+          <t>XX8302</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -11215,7 +10987,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>FR9193</t>
+          <t>XX9193</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -11228,9 +11000,6 @@
           <t>18:28</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
           <t>B738</t>
@@ -11248,12 +11017,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr"/>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>FR3914</t>
+          <t>XX3914</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -11285,7 +11051,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>FR5432</t>
+          <t>XX5432</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -11300,7 +11066,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>FR9912</t>
+          <t>XX9912</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -11332,7 +11098,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>FR1297</t>
+          <t>XX1297</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -11347,7 +11113,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>FR5103</t>
+          <t>XX5103</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -11379,7 +11145,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>FR1605</t>
+          <t>XX1605</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11392,9 +11158,6 @@
           <t>19:19</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
           <t>B738</t>
@@ -11412,12 +11175,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>FR1251</t>
+          <t>XX1251</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -11449,7 +11209,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>FR1302</t>
+          <t>XX1302</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -11464,7 +11224,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>FR9284</t>
+          <t>XX9284</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -11496,7 +11256,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>FR4104</t>
+          <t>XX4104</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -11511,7 +11271,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>FR9425</t>
+          <t>XX9425</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -11543,7 +11303,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>FR8778</t>
+          <t>XX8778</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -11556,9 +11316,6 @@
           <t>18:08</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -11576,12 +11333,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>FR5025</t>
+          <t>XX5025</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -11613,7 +11367,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>FR8324</t>
+          <t>XX8324</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -11628,7 +11382,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>FR2741</t>
+          <t>XX2741</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -11660,7 +11414,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>FR8080</t>
+          <t>XX8080</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -11675,7 +11429,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>FR9110</t>
+          <t>XX9110</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -11707,7 +11461,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>FR7440</t>
+          <t>XX7440</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -11720,9 +11474,6 @@
           <t>20:11</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -11740,12 +11491,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>FR9301</t>
+          <t>XX9301</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -11777,7 +11525,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>FR6042</t>
+          <t>XX6042</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -11792,7 +11540,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>FR4525</t>
+          <t>XX4525</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -11824,7 +11572,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>FR4761</t>
+          <t>XX4761</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -11839,7 +11587,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>FR6614</t>
+          <t>XX6614</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -11871,7 +11619,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>FR4254</t>
+          <t>XX4254</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -11884,9 +11632,6 @@
           <t>17:44</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -11904,12 +11649,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
-          <t>FR3289</t>
+          <t>XX3289</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -11941,7 +11683,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>FR7630</t>
+          <t>XX7630</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -11956,7 +11698,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>FR6694</t>
+          <t>XX6694</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -11988,7 +11730,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>FR1891</t>
+          <t>XX1891</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -12003,7 +11745,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>FR3126</t>
+          <t>XX3126</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -12035,7 +11777,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>FR9744</t>
+          <t>XX9744</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -12048,9 +11790,6 @@
           <t>20:43</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -12068,12 +11807,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t>FR2158</t>
+          <t>XX2158</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -12105,7 +11841,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>FR5187</t>
+          <t>XX5187</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -12120,7 +11856,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>FR8057</t>
+          <t>XX8057</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -12152,7 +11888,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>FR3674</t>
+          <t>XX3674</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -12167,7 +11903,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>FR1907</t>
+          <t>XX1907</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -12199,7 +11935,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>FR2384</t>
+          <t>XX2384</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -12212,9 +11948,6 @@
           <t>20:34</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -12232,12 +11965,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>FR7240</t>
+          <t>XX7240</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -12269,7 +11999,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>FR9289</t>
+          <t>XX9289</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -12284,7 +12014,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>FR9875</t>
+          <t>XX9875</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -12316,7 +12046,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>FR4968</t>
+          <t>XX4968</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -12331,7 +12061,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>FR5801</t>
+          <t>XX5801</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -12363,7 +12093,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>FR1741</t>
+          <t>XX1741</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -12376,9 +12106,6 @@
           <t>20:50</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
           <t>B738</t>
@@ -12396,12 +12123,9 @@
           <t>15/07/2027</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr"/>
-      <c r="C279" t="inlineStr"/>
-      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>FR8527</t>
+          <t>XX8527</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -12433,7 +12157,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>FR4036</t>
+          <t>XX4036</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -12448,7 +12172,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>FR3581</t>
+          <t>XX3581</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -12480,7 +12204,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>FR5407</t>
+          <t>XX5407</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -12495,7 +12219,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>FR8304</t>
+          <t>XX8304</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -12527,7 +12251,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>FR1059</t>
+          <t>XX1059</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -12542,7 +12266,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>FR5312</t>
+          <t>XX5312</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -12574,7 +12298,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>FR9835</t>
+          <t>XX9835</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -12589,7 +12313,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>FR6389</t>
+          <t>XX6389</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -12621,7 +12345,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>FR6300</t>
+          <t>XX6300</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -12636,7 +12360,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>FR5005</t>
+          <t>XX5005</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -12668,7 +12392,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>FR1564</t>
+          <t>XX1564</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -12683,7 +12407,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>FR6071</t>
+          <t>XX6071</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -12715,7 +12439,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>FR4569</t>
+          <t>XX4569</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -12730,7 +12454,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>FR9644</t>
+          <t>XX9644</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -12762,7 +12486,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>FR3997</t>
+          <t>XX3997</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -12777,7 +12501,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>FR1017</t>
+          <t>XX1017</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -12809,7 +12533,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>FR6494</t>
+          <t>XX6494</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -12824,7 +12548,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>FR7252</t>
+          <t>XX7252</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -12856,7 +12580,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>FR2374</t>
+          <t>XX2374</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -12871,7 +12595,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>FR8776</t>
+          <t>XX8776</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -12903,7 +12627,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>FR5569</t>
+          <t>XX5569</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -12918,7 +12642,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>FR9237</t>
+          <t>XX9237</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -12950,7 +12674,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>FR4292</t>
+          <t>XX4292</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12965,7 +12689,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>FR5066</t>
+          <t>XX5066</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -12997,7 +12721,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>FR9269</t>
+          <t>XX9269</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -13012,7 +12736,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>FR1081</t>
+          <t>XX1081</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -13044,7 +12768,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>FR2488</t>
+          <t>XX2488</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -13059,7 +12783,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>FR5328</t>
+          <t>XX5328</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -13091,7 +12815,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>FR2470</t>
+          <t>XX2470</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -13106,7 +12830,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>FR3357</t>
+          <t>XX3357</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -13138,7 +12862,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>FR7545</t>
+          <t>XX7545</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -13153,7 +12877,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>FR1682</t>
+          <t>XX1682</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -13185,7 +12909,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>FR7454</t>
+          <t>XX7454</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -13200,7 +12924,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>FR1368</t>
+          <t>XX1368</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -13232,7 +12956,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>FR5909</t>
+          <t>XX5909</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -13247,7 +12971,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>FR5984</t>
+          <t>XX5984</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -13279,7 +13003,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>FR4814</t>
+          <t>XX4814</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -13294,7 +13018,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>FR9542</t>
+          <t>XX9542</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -13326,7 +13050,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>FR3543</t>
+          <t>XX3543</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -13341,7 +13065,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>FR7381</t>
+          <t>XX7381</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -13373,7 +13097,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>FR6343</t>
+          <t>XX6343</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -13388,7 +13112,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>FR9096</t>
+          <t>XX9096</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -13420,7 +13144,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>FR3448</t>
+          <t>XX3448</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -13435,7 +13159,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>FR5655</t>
+          <t>XX5655</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -13467,7 +13191,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>FR3371</t>
+          <t>XX3371</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -13482,7 +13206,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>FR1717</t>
+          <t>XX1717</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -13514,7 +13238,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>FR9404</t>
+          <t>XX9404</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -13529,7 +13253,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>FR8032</t>
+          <t>XX8032</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -13561,7 +13285,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>FR9689</t>
+          <t>XX9689</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -13576,7 +13300,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>FR3282</t>
+          <t>XX3282</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -13608,7 +13332,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>FR9263</t>
+          <t>XX9263</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -13623,7 +13347,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>FR1263</t>
+          <t>XX1263</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -13655,7 +13379,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>FR4767</t>
+          <t>XX4767</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -13670,7 +13394,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>FR2394</t>
+          <t>XX2394</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -13702,7 +13426,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>FR1510</t>
+          <t>XX1510</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -13717,7 +13441,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>FR1685</t>
+          <t>XX1685</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -13749,7 +13473,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>FR3180</t>
+          <t>XX3180</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -13764,7 +13488,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>FR6909</t>
+          <t>XX6909</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -13796,7 +13520,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>FR2718</t>
+          <t>XX2718</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -13811,7 +13535,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>FR7170</t>
+          <t>XX7170</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -13843,7 +13567,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>FR8395</t>
+          <t>XX8395</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -13858,7 +13582,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>FR1831</t>
+          <t>XX1831</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -13890,7 +13614,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>FR1308</t>
+          <t>XX1308</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -13905,7 +13629,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>FR5006</t>
+          <t>XX5006</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -13935,12 +13659,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr"/>
-      <c r="C312" t="inlineStr"/>
-      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>FR9016</t>
+          <t>XX9016</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -13972,7 +13693,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>FR5321</t>
+          <t>XX5321</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -13987,7 +13708,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>FR1054</t>
+          <t>XX1054</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -14019,7 +13740,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>FR8486</t>
+          <t>XX8486</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -14034,7 +13755,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>FR2148</t>
+          <t>XX2148</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -14066,7 +13787,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>FR9240</t>
+          <t>XX9240</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -14079,9 +13800,6 @@
           <t>18:57</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
           <t>B738</t>
@@ -14099,12 +13817,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr"/>
-      <c r="C316" t="inlineStr"/>
-      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>FR2506</t>
+          <t>XX2506</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -14136,7 +13851,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>FR2082</t>
+          <t>XX2082</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -14151,7 +13866,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>FR8763</t>
+          <t>XX8763</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -14183,7 +13898,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>FR5131</t>
+          <t>XX5131</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -14198,7 +13913,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>FR2219</t>
+          <t>XX2219</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -14230,7 +13945,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>FR5350</t>
+          <t>XX5350</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -14245,7 +13960,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>FR4846</t>
+          <t>XX4846</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -14277,7 +13992,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>FR9817</t>
+          <t>XX9817</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -14290,9 +14005,6 @@
           <t>22:20</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
           <t>B738</t>
@@ -14310,12 +14022,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr"/>
-      <c r="C321" t="inlineStr"/>
-      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>FR9886</t>
+          <t>XX9886</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -14347,7 +14056,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>FR8542</t>
+          <t>XX8542</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -14362,7 +14071,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>FR9092</t>
+          <t>XX9092</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -14394,7 +14103,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>FR7267</t>
+          <t>XX7267</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -14409,7 +14118,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>FR2257</t>
+          <t>XX2257</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -14441,7 +14150,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>FR8848</t>
+          <t>XX8848</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -14454,9 +14163,6 @@
           <t>16:47</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -14474,12 +14180,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr"/>
-      <c r="C325" t="inlineStr"/>
-      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>FR5707</t>
+          <t>XX5707</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -14511,7 +14214,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>FR1765</t>
+          <t>XX1765</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -14526,7 +14229,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>FR4248</t>
+          <t>XX4248</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -14558,7 +14261,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>FR2269</t>
+          <t>XX2269</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -14573,7 +14276,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>FR3415</t>
+          <t>XX3415</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -14605,7 +14308,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>FR6435</t>
+          <t>XX6435</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -14618,9 +14321,6 @@
           <t>19:36</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr">
         <is>
           <t>B738</t>
@@ -14638,12 +14338,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr"/>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>FR5160</t>
+          <t>XX5160</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -14675,7 +14372,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>FR5987</t>
+          <t>XX5987</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -14690,7 +14387,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>FR3186</t>
+          <t>XX3186</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -14722,7 +14419,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>FR1204</t>
+          <t>XX1204</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -14737,7 +14434,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>FR8903</t>
+          <t>XX8903</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -14769,7 +14466,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>FR1993</t>
+          <t>XX1993</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -14782,9 +14479,6 @@
           <t>17:40</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr">
         <is>
           <t>B738</t>
@@ -14802,12 +14496,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr"/>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>FR8959</t>
+          <t>XX8959</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -14839,7 +14530,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>FR5403</t>
+          <t>XX5403</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -14854,7 +14545,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>FR2630</t>
+          <t>XX2630</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -14886,7 +14577,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>FR4566</t>
+          <t>XX4566</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -14901,7 +14592,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>FR9021</t>
+          <t>XX9021</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -14933,7 +14624,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>FR5765</t>
+          <t>XX5765</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -14946,9 +14637,6 @@
           <t>19:16</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr">
         <is>
           <t>B738</t>
@@ -14966,12 +14654,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr"/>
-      <c r="C337" t="inlineStr"/>
-      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>FR5678</t>
+          <t>XX5678</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -15003,7 +14688,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>FR8613</t>
+          <t>XX8613</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -15018,7 +14703,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>FR8633</t>
+          <t>XX8633</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -15050,7 +14735,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>FR8640</t>
+          <t>XX8640</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -15065,7 +14750,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>FR2941</t>
+          <t>XX2941</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -15097,7 +14782,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>FR4264</t>
+          <t>XX4264</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -15110,9 +14795,6 @@
           <t>20:28</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -15130,12 +14812,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr"/>
-      <c r="C341" t="inlineStr"/>
-      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>FR6106</t>
+          <t>XX6106</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -15167,7 +14846,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>FR2406</t>
+          <t>XX2406</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -15182,7 +14861,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>FR8748</t>
+          <t>XX8748</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -15214,7 +14893,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>FR1286</t>
+          <t>XX1286</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -15229,7 +14908,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>FR9970</t>
+          <t>XX9970</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -15261,7 +14940,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>FR8519</t>
+          <t>XX8519</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -15274,9 +14953,6 @@
           <t>19:00</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
       <c r="H344" t="inlineStr">
         <is>
           <t>B738</t>
@@ -15294,12 +14970,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr"/>
-      <c r="C345" t="inlineStr"/>
-      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>FR2252</t>
+          <t>XX2252</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -15331,7 +15004,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>FR9300</t>
+          <t>XX9300</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -15346,7 +15019,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>FR8363</t>
+          <t>XX8363</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -15378,7 +15051,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>FR5401</t>
+          <t>XX5401</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -15393,7 +15066,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>FR7338</t>
+          <t>XX7338</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -15425,7 +15098,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>FR4437</t>
+          <t>XX4437</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -15438,9 +15111,6 @@
           <t>19:44</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr">
         <is>
           <t>B738</t>
@@ -15458,12 +15128,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr"/>
-      <c r="C349" t="inlineStr"/>
-      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>FR4452</t>
+          <t>XX4452</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -15495,7 +15162,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>FR2222</t>
+          <t>XX2222</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -15510,7 +15177,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>FR2479</t>
+          <t>XX2479</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -15542,7 +15209,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>FR3322</t>
+          <t>XX3322</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -15557,7 +15224,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>FR5289</t>
+          <t>XX5289</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -15589,7 +15256,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>FR6890</t>
+          <t>XX6890</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -15602,9 +15269,6 @@
           <t>19:38</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr">
         <is>
           <t>B738</t>
@@ -15622,12 +15286,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr"/>
-      <c r="C353" t="inlineStr"/>
-      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>FR3172</t>
+          <t>XX3172</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -15659,7 +15320,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>FR9335</t>
+          <t>XX9335</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -15674,7 +15335,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>FR5580</t>
+          <t>XX5580</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -15706,7 +15367,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>FR2846</t>
+          <t>XX2846</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -15721,7 +15382,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>FR6983</t>
+          <t>XX6983</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -15753,7 +15414,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>FR4790</t>
+          <t>XX4790</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -15766,9 +15427,6 @@
           <t>19:21</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -15786,12 +15444,9 @@
           <t>16/07/2027</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr"/>
-      <c r="C357" t="inlineStr"/>
-      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>FR9157</t>
+          <t>XX9157</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -15823,7 +15478,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>FR8964</t>
+          <t>XX8964</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -15838,7 +15493,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>FR7456</t>
+          <t>XX7456</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -15870,7 +15525,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>FR1406</t>
+          <t>XX1406</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -15885,7 +15540,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>FR3606</t>
+          <t>XX3606</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -15917,7 +15572,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>FR1058</t>
+          <t>XX1058</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -15930,9 +15585,6 @@
           <t>19:05</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
-      <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr">
         <is>
           <t>B738</t>
@@ -15952,7 +15604,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>FR9055</t>
+          <t>XX9055</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -15967,7 +15619,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>FR8385</t>
+          <t>XX8385</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -15999,7 +15651,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>FR7642</t>
+          <t>XX7642</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -16014,7 +15666,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>FR5947</t>
+          <t>XX5947</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -16046,7 +15698,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>FR3305</t>
+          <t>XX3305</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -16061,7 +15713,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>FR7818</t>
+          <t>XX7818</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -16093,7 +15745,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>FR6635</t>
+          <t>XX6635</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -16108,7 +15760,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>FR7162</t>
+          <t>XX7162</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -16140,7 +15792,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>FR6178</t>
+          <t>XX6178</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -16155,7 +15807,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>FR2980</t>
+          <t>XX2980</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -16187,7 +15839,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>FR6428</t>
+          <t>XX6428</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -16202,7 +15854,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>FR1028</t>
+          <t>XX1028</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -16234,7 +15886,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>FR6317</t>
+          <t>XX6317</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -16249,7 +15901,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>FR6542</t>
+          <t>XX6542</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -16281,7 +15933,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>FR9655</t>
+          <t>XX9655</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -16296,7 +15948,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>FR2966</t>
+          <t>XX2966</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -16328,7 +15980,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>FR9645</t>
+          <t>XX9645</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -16343,7 +15995,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>FR1192</t>
+          <t>XX1192</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -16375,7 +16027,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>FR5748</t>
+          <t>XX5748</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -16390,7 +16042,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>FR5148</t>
+          <t>XX5148</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -16422,7 +16074,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>FR7098</t>
+          <t>XX7098</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -16437,7 +16089,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>FR9918</t>
+          <t>XX9918</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -16469,7 +16121,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>FR7437</t>
+          <t>XX7437</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -16484,7 +16136,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>FR7392</t>
+          <t>XX7392</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -16516,7 +16168,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>FR2251</t>
+          <t>XX2251</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -16531,7 +16183,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>FR9633</t>
+          <t>XX9633</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -16563,7 +16215,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>FR8013</t>
+          <t>XX8013</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -16578,7 +16230,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>FR5508</t>
+          <t>XX5508</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -16610,7 +16262,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>FR1790</t>
+          <t>XX1790</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -16625,7 +16277,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>FR5597</t>
+          <t>XX5597</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -16657,7 +16309,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>FR2666</t>
+          <t>XX2666</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -16672,7 +16324,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>FR1845</t>
+          <t>XX1845</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -16704,7 +16356,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>FR5679</t>
+          <t>XX5679</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -16719,7 +16371,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>FR3439</t>
+          <t>XX3439</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -16751,7 +16403,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>FR5084</t>
+          <t>XX5084</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -16766,7 +16418,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>FR5353</t>
+          <t>XX5353</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -16798,7 +16450,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>FR8147</t>
+          <t>XX8147</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -16813,7 +16465,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>FR6170</t>
+          <t>XX6170</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -16845,7 +16497,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>FR4110</t>
+          <t>XX4110</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -16860,7 +16512,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>FR7116</t>
+          <t>XX7116</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -16892,7 +16544,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>FR8008</t>
+          <t>XX8008</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -16907,7 +16559,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>FR1475</t>
+          <t>XX1475</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -16939,7 +16591,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>FR7554</t>
+          <t>XX7554</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -16954,7 +16606,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>FR4333</t>
+          <t>XX4333</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -16986,7 +16638,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>FR9897</t>
+          <t>XX9897</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -17001,7 +16653,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>FR1810</t>
+          <t>XX1810</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -17033,7 +16685,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>FR7731</t>
+          <t>XX7731</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -17048,7 +16700,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>FR8386</t>
+          <t>XX8386</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -17080,7 +16732,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>FR3270</t>
+          <t>XX3270</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -17095,7 +16747,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>FR5689</t>
+          <t>XX5689</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -17127,7 +16779,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>FR8955</t>
+          <t>XX8955</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -17142,7 +16794,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>FR1802</t>
+          <t>XX1802</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -17174,7 +16826,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>FR3085</t>
+          <t>XX3085</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -17189,7 +16841,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>FR3797</t>
+          <t>XX3797</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -17221,7 +16873,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>FR8736</t>
+          <t>XX8736</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -17236,7 +16888,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>FR7797</t>
+          <t>XX7797</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -17268,7 +16920,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>FR6630</t>
+          <t>XX6630</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -17283,7 +16935,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>FR5616</t>
+          <t>XX5616</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -17315,7 +16967,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>FR5878</t>
+          <t>XX5878</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -17330,7 +16982,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>FR5190</t>
+          <t>XX5190</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -17360,12 +17012,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr"/>
-      <c r="C391" t="inlineStr"/>
-      <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
-          <t>FR5262</t>
+          <t>XX5262</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -17397,7 +17046,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>FR7655</t>
+          <t>XX7655</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -17412,7 +17061,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>FR4910</t>
+          <t>XX4910</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -17444,7 +17093,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>FR5928</t>
+          <t>XX5928</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -17459,7 +17108,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>FR8916</t>
+          <t>XX8916</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -17491,7 +17140,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>FR7461</t>
+          <t>XX7461</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -17504,9 +17153,6 @@
           <t>20:07</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -17524,12 +17170,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr"/>
-      <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
-          <t>FR2961</t>
+          <t>XX2961</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -17561,7 +17204,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>FR3741</t>
+          <t>XX3741</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -17576,7 +17219,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>FR3648</t>
+          <t>XX3648</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -17608,7 +17251,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>FR2231</t>
+          <t>XX2231</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -17623,7 +17266,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>FR4405</t>
+          <t>XX4405</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -17655,7 +17298,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>FR9201</t>
+          <t>XX9201</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -17668,9 +17311,6 @@
           <t>20:24</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr">
         <is>
           <t>B738</t>
@@ -17688,12 +17328,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr"/>
-      <c r="C399" t="inlineStr"/>
-      <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr">
         <is>
-          <t>FR9144</t>
+          <t>XX9144</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -17725,7 +17362,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>FR4604</t>
+          <t>XX4604</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -17740,7 +17377,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>FR8421</t>
+          <t>XX8421</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -17772,7 +17409,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>FR6453</t>
+          <t>XX6453</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -17787,7 +17424,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>FR8372</t>
+          <t>XX8372</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -17819,7 +17456,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>FR8002</t>
+          <t>XX8002</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -17832,9 +17469,6 @@
           <t>19:11</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
           <t>B738</t>
@@ -17852,12 +17486,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr"/>
-      <c r="C403" t="inlineStr"/>
-      <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
-          <t>FR3287</t>
+          <t>XX3287</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -17889,7 +17520,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>FR4152</t>
+          <t>XX4152</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -17904,7 +17535,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>FR9946</t>
+          <t>XX9946</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -17936,7 +17567,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>FR9981</t>
+          <t>XX9981</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -17951,7 +17582,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>FR3862</t>
+          <t>XX3862</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -17983,7 +17614,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>FR6602</t>
+          <t>XX6602</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -17996,9 +17627,6 @@
           <t>18:54</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -18016,12 +17644,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr"/>
-      <c r="C407" t="inlineStr"/>
-      <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr">
         <is>
-          <t>FR2492</t>
+          <t>XX2492</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -18053,7 +17678,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>FR6231</t>
+          <t>XX6231</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -18068,7 +17693,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>FR4917</t>
+          <t>XX4917</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -18100,7 +17725,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>FR7034</t>
+          <t>XX7034</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -18115,7 +17740,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>FR5232</t>
+          <t>XX5232</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -18147,7 +17772,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>FR4311</t>
+          <t>XX4311</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -18160,9 +17785,6 @@
           <t>17:47</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr"/>
       <c r="H410" t="inlineStr">
         <is>
           <t>B738</t>
@@ -18180,12 +17802,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr"/>
-      <c r="C411" t="inlineStr"/>
-      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>FR1329</t>
+          <t>XX1329</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -18217,7 +17836,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>FR7763</t>
+          <t>XX7763</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -18232,7 +17851,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>FR7272</t>
+          <t>XX7272</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -18264,7 +17883,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>FR7781</t>
+          <t>XX7781</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -18279,7 +17898,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>FR4440</t>
+          <t>XX4440</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -18311,7 +17930,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>FR7174</t>
+          <t>XX7174</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -18324,9 +17943,6 @@
           <t>18:02</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr"/>
       <c r="H414" t="inlineStr">
         <is>
           <t>B738</t>
@@ -18344,12 +17960,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr"/>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>FR5427</t>
+          <t>XX5427</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -18381,7 +17994,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>FR6541</t>
+          <t>XX6541</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -18396,7 +18009,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>FR2016</t>
+          <t>XX2016</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -18428,7 +18041,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>FR9161</t>
+          <t>XX9161</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -18443,7 +18056,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>FR5546</t>
+          <t>XX5546</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -18475,7 +18088,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>FR6900</t>
+          <t>XX6900</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -18488,9 +18101,6 @@
           <t>20:41</t>
         </is>
       </c>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr">
         <is>
           <t>B738</t>
@@ -18508,12 +18118,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr"/>
-      <c r="C419" t="inlineStr"/>
-      <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr">
         <is>
-          <t>FR3062</t>
+          <t>XX3062</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -18545,7 +18152,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>FR9247</t>
+          <t>XX9247</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -18560,7 +18167,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>FR4538</t>
+          <t>XX4538</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -18592,7 +18199,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>FR2517</t>
+          <t>XX2517</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -18607,7 +18214,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>FR5440</t>
+          <t>XX5440</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -18639,7 +18246,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>FR9948</t>
+          <t>XX9948</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -18652,9 +18259,6 @@
           <t>19:40</t>
         </is>
       </c>
-      <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr"/>
       <c r="H422" t="inlineStr">
         <is>
           <t>B738</t>
@@ -18672,12 +18276,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr"/>
-      <c r="C423" t="inlineStr"/>
-      <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>FR7300</t>
+          <t>XX7300</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -18709,7 +18310,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>FR7549</t>
+          <t>XX7549</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -18724,7 +18325,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>FR9531</t>
+          <t>XX9531</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -18756,7 +18357,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>FR8075</t>
+          <t>XX8075</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -18771,7 +18372,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>FR6112</t>
+          <t>XX6112</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -18803,7 +18404,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>FR1357</t>
+          <t>XX1357</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -18816,9 +18417,6 @@
           <t>21:39</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -18836,12 +18434,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr"/>
-      <c r="C427" t="inlineStr"/>
-      <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>FR3084</t>
+          <t>XX3084</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -18873,7 +18468,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>FR1528</t>
+          <t>XX1528</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -18888,7 +18483,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>FR7966</t>
+          <t>XX7966</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -18920,7 +18515,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>FR8754</t>
+          <t>XX8754</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -18935,7 +18530,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>FR9025</t>
+          <t>XX9025</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -18967,7 +18562,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>FR1002</t>
+          <t>XX1002</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -18980,9 +18575,6 @@
           <t>20:54</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr">
         <is>
           <t>B738</t>
@@ -19000,12 +18592,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr"/>
-      <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>FR9667</t>
+          <t>XX9667</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -19037,7 +18626,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>FR7414</t>
+          <t>XX7414</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -19052,7 +18641,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>FR8670</t>
+          <t>XX8670</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -19084,7 +18673,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>FR8355</t>
+          <t>XX8355</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -19099,7 +18688,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>FR9540</t>
+          <t>XX9540</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -19131,7 +18720,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>FR2786</t>
+          <t>XX2786</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -19144,9 +18733,6 @@
           <t>20:37</t>
         </is>
       </c>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
           <t>B738</t>
@@ -19164,12 +18750,9 @@
           <t>17/07/2027</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr"/>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>FR4666</t>
+          <t>XX4666</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -19201,7 +18784,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>FR3529</t>
+          <t>XX3529</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -19216,7 +18799,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>FR3491</t>
+          <t>XX3491</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -19248,7 +18831,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>FR2784</t>
+          <t>XX2784</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -19263,7 +18846,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>FR8492</t>
+          <t>XX8492</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -19295,7 +18878,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>FR2392</t>
+          <t>XX2392</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -19308,9 +18891,6 @@
           <t>19:08</t>
         </is>
       </c>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr">
         <is>
           <t>B738</t>
@@ -19330,7 +18910,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>FR1647</t>
+          <t>XX1647</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -19345,7 +18925,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>FR1022</t>
+          <t>XX1022</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -19377,7 +18957,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>FR3058</t>
+          <t>XX3058</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -19392,7 +18972,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>FR4810</t>
+          <t>XX4810</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -19424,7 +19004,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>FR1615</t>
+          <t>XX1615</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -19439,7 +19019,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>FR5977</t>
+          <t>XX5977</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -19471,7 +19051,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>FR3096</t>
+          <t>XX3096</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -19486,7 +19066,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>FR5125</t>
+          <t>XX5125</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -19518,7 +19098,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>FR8166</t>
+          <t>XX8166</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -19533,7 +19113,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>FR2837</t>
+          <t>XX2837</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -19565,7 +19145,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>FR2629</t>
+          <t>XX2629</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -19580,7 +19160,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>FR9841</t>
+          <t>XX9841</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -19612,7 +19192,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>FR5920</t>
+          <t>XX5920</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -19627,7 +19207,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>FR4140</t>
+          <t>XX4140</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -19659,7 +19239,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>FR7358</t>
+          <t>XX7358</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -19674,7 +19254,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>FR5274</t>
+          <t>XX5274</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -19706,7 +19286,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>FR4663</t>
+          <t>XX4663</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -19721,7 +19301,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>FR1018</t>
+          <t>XX1018</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -19753,7 +19333,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>FR1171</t>
+          <t>XX1171</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -19768,7 +19348,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>FR5940</t>
+          <t>XX5940</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -19800,7 +19380,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>FR8547</t>
+          <t>XX8547</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -19815,7 +19395,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>FR5564</t>
+          <t>XX5564</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -19847,7 +19427,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>FR6183</t>
+          <t>XX6183</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -19862,7 +19442,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>FR4970</t>
+          <t>XX4970</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -19894,7 +19474,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>FR8787</t>
+          <t>XX8787</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -19909,7 +19489,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>FR9458</t>
+          <t>XX9458</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -19941,7 +19521,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>FR5047</t>
+          <t>XX5047</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -19956,7 +19536,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>FR1479</t>
+          <t>XX1479</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -19988,7 +19568,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>FR7747</t>
+          <t>XX7747</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -20003,7 +19583,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>FR6036</t>
+          <t>XX6036</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -20035,7 +19615,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>FR1906</t>
+          <t>XX1906</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -20050,7 +19630,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>FR1356</t>
+          <t>XX1356</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -20082,7 +19662,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>FR4180</t>
+          <t>XX4180</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -20097,7 +19677,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>FR9164</t>
+          <t>XX9164</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -20129,7 +19709,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>FR7881</t>
+          <t>XX7881</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -20144,7 +19724,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>FR2328</t>
+          <t>XX2328</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -20176,7 +19756,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>FR5214</t>
+          <t>XX5214</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -20191,7 +19771,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>FR4732</t>
+          <t>XX4732</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -20223,7 +19803,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>FR7952</t>
+          <t>XX7952</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -20238,7 +19818,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>FR7065</t>
+          <t>XX7065</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
@@ -20270,7 +19850,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>FR4715</t>
+          <t>XX4715</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -20285,7 +19865,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>FR9076</t>
+          <t>XX9076</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -20317,7 +19897,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>FR1558</t>
+          <t>XX1558</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -20332,7 +19912,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>FR6538</t>
+          <t>XX6538</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -20364,7 +19944,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>FR7890</t>
+          <t>XX7890</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -20379,7 +19959,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>FR6936</t>
+          <t>XX6936</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -20411,7 +19991,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>FR7493</t>
+          <t>XX7493</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -20426,7 +20006,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>FR4245</t>
+          <t>XX4245</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -20458,7 +20038,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>FR1110</t>
+          <t>XX1110</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -20473,7 +20053,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>FR5785</t>
+          <t>XX5785</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -20505,7 +20085,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>FR2104</t>
+          <t>XX2104</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -20520,7 +20100,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>FR9457</t>
+          <t>XX9457</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -20552,7 +20132,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>FR9121</t>
+          <t>XX9121</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -20567,7 +20147,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>FR4283</t>
+          <t>XX4283</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -20599,7 +20179,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>FR6107</t>
+          <t>XX6107</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -20614,7 +20194,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>FR4177</t>
+          <t>XX4177</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -20646,7 +20226,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>FR4781</t>
+          <t>XX4781</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -20661,7 +20241,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>FR8620</t>
+          <t>XX8620</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -20693,7 +20273,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>FR4628</t>
+          <t>XX4628</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -20708,7 +20288,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>FR5342</t>
+          <t>XX5342</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -20738,12 +20318,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr"/>
-      <c r="C469" t="inlineStr"/>
-      <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr">
         <is>
-          <t>FR5832</t>
+          <t>XX5832</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -20775,7 +20352,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>FR2785</t>
+          <t>XX2785</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -20790,7 +20367,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>FR9122</t>
+          <t>XX9122</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -20822,7 +20399,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>FR4068</t>
+          <t>XX4068</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -20837,7 +20414,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>FR4658</t>
+          <t>XX4658</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -20869,7 +20446,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>FR8947</t>
+          <t>XX8947</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -20882,9 +20459,6 @@
           <t>20:12</t>
         </is>
       </c>
-      <c r="E472" t="inlineStr"/>
-      <c r="F472" t="inlineStr"/>
-      <c r="G472" t="inlineStr"/>
       <c r="H472" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -20902,12 +20476,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr"/>
-      <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t>FR7832</t>
+          <t>XX7832</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -20939,7 +20510,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>FR1924</t>
+          <t>XX1924</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -20954,7 +20525,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>FR3398</t>
+          <t>XX3398</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -20986,7 +20557,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>FR7446</t>
+          <t>XX7446</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -21001,7 +20572,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>FR1890</t>
+          <t>XX1890</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -21033,7 +20604,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>FR4488</t>
+          <t>XX4488</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -21046,9 +20617,6 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="E476" t="inlineStr"/>
-      <c r="F476" t="inlineStr"/>
-      <c r="G476" t="inlineStr"/>
       <c r="H476" t="inlineStr">
         <is>
           <t>B738</t>
@@ -21066,12 +20634,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B477" t="inlineStr"/>
-      <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>FR1387</t>
+          <t>XX1387</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -21103,7 +20668,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>FR3325</t>
+          <t>XX3325</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -21118,7 +20683,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>FR4402</t>
+          <t>XX4402</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -21150,7 +20715,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>FR1424</t>
+          <t>XX1424</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -21165,7 +20730,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>FR6815</t>
+          <t>XX6815</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -21197,7 +20762,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>FR1492</t>
+          <t>XX1492</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -21210,9 +20775,6 @@
           <t>20:25</t>
         </is>
       </c>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
-      <c r="G480" t="inlineStr"/>
       <c r="H480" t="inlineStr">
         <is>
           <t>B738</t>
@@ -21230,12 +20792,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr"/>
-      <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>FR2508</t>
+          <t>XX2508</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -21267,7 +20826,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>FR9776</t>
+          <t>XX9776</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -21282,7 +20841,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>FR4683</t>
+          <t>XX4683</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -21314,7 +20873,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>FR8357</t>
+          <t>XX8357</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -21329,7 +20888,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>FR6832</t>
+          <t>XX6832</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -21361,7 +20920,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>FR8238</t>
+          <t>XX8238</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -21374,9 +20933,6 @@
           <t>20:24</t>
         </is>
       </c>
-      <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
-      <c r="G484" t="inlineStr"/>
       <c r="H484" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -21394,12 +20950,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr"/>
-      <c r="C485" t="inlineStr"/>
-      <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr">
         <is>
-          <t>FR3573</t>
+          <t>XX3573</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -21431,7 +20984,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>FR7002</t>
+          <t>XX7002</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -21446,7 +20999,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>FR1927</t>
+          <t>XX1927</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -21478,7 +21031,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>FR9171</t>
+          <t>XX9171</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -21493,7 +21046,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>FR1650</t>
+          <t>XX1650</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -21525,7 +21078,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>FR8631</t>
+          <t>XX8631</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -21538,9 +21091,6 @@
           <t>17:36</t>
         </is>
       </c>
-      <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
-      <c r="G488" t="inlineStr"/>
       <c r="H488" t="inlineStr">
         <is>
           <t>B738</t>
@@ -21558,12 +21108,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr"/>
-      <c r="C489" t="inlineStr"/>
-      <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr">
         <is>
-          <t>FR2356</t>
+          <t>XX2356</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -21595,7 +21142,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>FR3697</t>
+          <t>XX3697</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -21610,7 +21157,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>FR2562</t>
+          <t>XX2562</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -21642,7 +21189,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>FR2519</t>
+          <t>XX2519</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -21657,7 +21204,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>FR6345</t>
+          <t>XX6345</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -21689,7 +21236,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>FR8666</t>
+          <t>XX8666</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -21702,9 +21249,6 @@
           <t>19:56</t>
         </is>
       </c>
-      <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
-      <c r="G492" t="inlineStr"/>
       <c r="H492" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -21722,12 +21266,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr"/>
-      <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>FR5299</t>
+          <t>XX5299</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -21759,7 +21300,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>FR7113</t>
+          <t>XX7113</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -21774,7 +21315,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>FR4830</t>
+          <t>XX4830</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -21806,7 +21347,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>FR1261</t>
+          <t>XX1261</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -21821,7 +21362,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>FR9747</t>
+          <t>XX9747</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -21853,7 +21394,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>FR6443</t>
+          <t>XX6443</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -21866,9 +21407,6 @@
           <t>19:33</t>
         </is>
       </c>
-      <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
-      <c r="G496" t="inlineStr"/>
       <c r="H496" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -21886,12 +21424,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B497" t="inlineStr"/>
-      <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>FR6942</t>
+          <t>XX6942</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -21923,7 +21458,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>FR4101</t>
+          <t>XX4101</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -21938,7 +21473,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>FR7874</t>
+          <t>XX7874</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -21970,7 +21505,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>FR4062</t>
+          <t>XX4062</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -21985,7 +21520,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>FR9068</t>
+          <t>XX9068</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -22017,7 +21552,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>FR3717</t>
+          <t>XX3717</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -22030,9 +21565,6 @@
           <t>19:55</t>
         </is>
       </c>
-      <c r="E500" t="inlineStr"/>
-      <c r="F500" t="inlineStr"/>
-      <c r="G500" t="inlineStr"/>
       <c r="H500" t="inlineStr">
         <is>
           <t>B738</t>
@@ -22050,12 +21582,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B501" t="inlineStr"/>
-      <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>FR4624</t>
+          <t>XX4624</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -22087,7 +21616,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>FR2386</t>
+          <t>XX2386</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -22102,7 +21631,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>FR1892</t>
+          <t>XX1892</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
@@ -22134,7 +21663,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>FR1023</t>
+          <t>XX1023</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -22149,7 +21678,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>FR1640</t>
+          <t>XX1640</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -22181,7 +21710,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>FR3292</t>
+          <t>XX3292</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -22194,9 +21723,6 @@
           <t>19:57</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
-      <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr">
         <is>
           <t>B738</t>
@@ -22214,12 +21740,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B505" t="inlineStr"/>
-      <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>FR1661</t>
+          <t>XX1661</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -22251,7 +21774,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>FR3879</t>
+          <t>XX3879</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -22266,7 +21789,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>FR4442</t>
+          <t>XX4442</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
@@ -22298,7 +21821,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>FR8827</t>
+          <t>XX8827</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -22313,7 +21836,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>FR8251</t>
+          <t>XX8251</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
@@ -22345,7 +21868,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>FR9976</t>
+          <t>XX9976</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -22360,7 +21883,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>FR5596</t>
+          <t>XX5596</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
@@ -22392,7 +21915,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>FR8899</t>
+          <t>XX8899</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -22405,9 +21928,6 @@
           <t>22:01</t>
         </is>
       </c>
-      <c r="E509" t="inlineStr"/>
-      <c r="F509" t="inlineStr"/>
-      <c r="G509" t="inlineStr"/>
       <c r="H509" t="inlineStr">
         <is>
           <t>B738</t>
@@ -22425,12 +21945,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B510" t="inlineStr"/>
-      <c r="C510" t="inlineStr"/>
-      <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>FR7216</t>
+          <t>XX7216</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -22462,7 +21979,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>FR2699</t>
+          <t>XX2699</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -22477,7 +21994,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>FR4114</t>
+          <t>XX4114</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -22509,7 +22026,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>FR3921</t>
+          <t>XX3921</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -22524,7 +22041,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>FR9635</t>
+          <t>XX9635</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -22554,12 +22071,9 @@
           <t>18/07/2027</t>
         </is>
       </c>
-      <c r="B513" t="inlineStr"/>
-      <c r="C513" t="inlineStr"/>
-      <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr">
         <is>
-          <t>FR7730</t>
+          <t>XX7730</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -22591,7 +22105,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>FR3528</t>
+          <t>XX3528</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -22606,7 +22120,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>FR7733</t>
+          <t>XX7733</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -22638,7 +22152,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>FR7585</t>
+          <t>XX7585</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -22653,7 +22167,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>FR4542</t>
+          <t>XX4542</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
@@ -22685,7 +22199,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>FR1718</t>
+          <t>XX1718</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -22698,9 +22212,6 @@
           <t>20:18</t>
         </is>
       </c>
-      <c r="E516" t="inlineStr"/>
-      <c r="F516" t="inlineStr"/>
-      <c r="G516" t="inlineStr"/>
       <c r="H516" t="inlineStr">
         <is>
           <t>B38M</t>
@@ -22720,7 +22231,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>FR1403</t>
+          <t>XX1403</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -22735,7 +22246,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>FR6777</t>
+          <t>XX6777</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -22767,7 +22278,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>FR4878</t>
+          <t>XX4878</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -22782,7 +22293,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>FR2603</t>
+          <t>XX2603</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -22814,7 +22325,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>FR4053</t>
+          <t>XX4053</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -22829,7 +22340,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>FR5436</t>
+          <t>XX5436</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
@@ -22861,7 +22372,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>FR8532</t>
+          <t>XX8532</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -22876,7 +22387,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>FR4656</t>
+          <t>XX4656</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
@@ -22908,7 +22419,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>FR2581</t>
+          <t>XX2581</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -22923,7 +22434,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>FR9328</t>
+          <t>XX9328</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
@@ -22955,7 +22466,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>FR3983</t>
+          <t>XX3983</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -22970,7 +22481,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>FR7040</t>
+          <t>XX7040</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
@@ -23002,7 +22513,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>FR8348</t>
+          <t>XX8348</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -23017,7 +22528,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>FR4887</t>
+          <t>XX4887</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
@@ -23049,7 +22560,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>FR1248</t>
+          <t>XX1248</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -23064,7 +22575,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>FR6174</t>
+          <t>XX6174</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -23096,7 +22607,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>FR4365</t>
+          <t>XX4365</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -23111,7 +22622,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>FR3031</t>
+          <t>XX3031</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
@@ -23143,7 +22654,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>FR7650</t>
+          <t>XX7650</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -23158,7 +22669,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>FR6123</t>
+          <t>XX6123</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -23190,7 +22701,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>FR7280</t>
+          <t>XX7280</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -23205,7 +22716,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>FR4315</t>
+          <t>XX4315</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
@@ -23237,7 +22748,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>FR1333</t>
+          <t>XX1333</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -23252,7 +22763,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>FR4076</t>
+          <t>XX4076</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
@@ -23284,7 +22795,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>FR1285</t>
+          <t>XX1285</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -23299,7 +22810,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>FR4801</t>
+          <t>XX4801</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
@@ -23331,7 +22842,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>FR1512</t>
+          <t>XX1512</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -23346,7 +22857,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>FR9894</t>
+          <t>XX9894</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
@@ -23378,7 +22889,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>FR8537</t>
+          <t>XX8537</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -23393,7 +22904,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>FR1507</t>
+          <t>XX1507</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -23425,7 +22936,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>FR3105</t>
+          <t>XX3105</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -23440,7 +22951,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>FR9960</t>
+          <t>XX9960</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
@@ -23472,7 +22983,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>FR7121</t>
+          <t>XX7121</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -23487,7 +22998,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>FR1514</t>
+          <t>XX1514</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
@@ -23519,7 +23030,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>FR8360</t>
+          <t>XX8360</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -23534,7 +23045,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>FR5961</t>
+          <t>XX5961</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
@@ -23566,7 +23077,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>FR3777</t>
+          <t>XX3777</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -23581,7 +23092,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>FR3973</t>
+          <t>XX3973</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
@@ -23613,7 +23124,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>FR3230</t>
+          <t>XX3230</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -23628,7 +23139,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>FR3744</t>
+          <t>XX3744</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
@@ -23660,7 +23171,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>FR8845</t>
+          <t>XX8845</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -23675,7 +23186,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>FR8813</t>
+          <t>XX8813</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
@@ -23707,7 +23218,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>FR9965</t>
+          <t>XX9965</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -23722,7 +23233,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>FR9283</t>
+          <t>XX9283</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
@@ -23754,7 +23265,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>FR9728</t>
+          <t>XX9728</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -23769,7 +23280,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>FR7114</t>
+          <t>XX7114</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
@@ -23801,7 +23312,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>FR6870</t>
+          <t>XX6870</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -23816,7 +23327,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>FR6649</t>
+          <t>XX6649</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
@@ -23848,7 +23359,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>FR3592</t>
+          <t>XX3592</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -23863,7 +23374,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>FR8571</t>
+          <t>XX8571</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
@@ -23895,7 +23406,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>FR3257</t>
+          <t>XX3257</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -23910,7 +23421,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>FR3436</t>
+          <t>XX3436</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
@@ -23942,7 +23453,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>FR1030</t>
+          <t>XX1030</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -23957,7 +23468,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>FR6911</t>
+          <t>XX6911</t>
         </is>
       </c>
       <c r="F543" t="inlineStr">
@@ -23989,7 +23500,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>FR7190</t>
+          <t>XX7190</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -24004,7 +23515,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>FR9338</t>
+          <t>XX9338</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -24036,7 +23547,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>FR8507</t>
+          <t>XX8507</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -24051,7 +23562,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>FR7599</t>
+          <t>XX7599</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
@@ -24083,7 +23594,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>FR6193</t>
+          <t>XX6193</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -24098,7 +23609,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>FR8753</t>
+          <t>XX8753</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
